--- a/Таблица.xlsx
+++ b/Таблица.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e48f6d8d52502f76/Рабочий стол/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_AD4DF75460589B3ACB7284494F587EB65BDEDDA5" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{164E8A40-CD24-493B-BE9C-3524806DB6F7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D101BF9E-D7E4-41CE-89B6-6540200CD31D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
-  <si>
-    <t>Год</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>Административный округ</t>
   </si>
@@ -418,18 +415,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -443,209 +439,176 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>2023</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="1">
+        <v>150</v>
+      </c>
+      <c r="D2" s="1">
+        <v>82</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1">
-        <v>150</v>
-      </c>
-      <c r="E2" s="1">
-        <v>82</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>2023</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
+      <c r="C3" s="1">
+        <v>140</v>
       </c>
       <c r="D3" s="1">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="E3" s="1">
-        <v>79</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>2024</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
+      <c r="C4" s="1">
+        <v>220</v>
       </c>
       <c r="D4" s="1">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="E4" s="1">
-        <v>85</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>2024</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="1">
+        <v>95</v>
+      </c>
+      <c r="D5" s="1">
+        <v>71</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="D5" s="1">
-        <v>95</v>
-      </c>
-      <c r="E5" s="1">
-        <v>71</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>2024</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="1">
+        <v>35</v>
+      </c>
+      <c r="D6" s="1">
+        <v>55</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="1">
-        <v>35</v>
-      </c>
-      <c r="E6" s="1">
-        <v>55</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="C7" s="1">
+        <v>60</v>
+      </c>
+      <c r="D7" s="1">
+        <v>45</v>
+      </c>
+      <c r="E7" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D7" s="1">
-        <v>60</v>
-      </c>
-      <c r="E7" s="1">
-        <v>45</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>2025</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="1">
+        <v>40</v>
+      </c>
+      <c r="D8" s="1">
+        <v>48</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="D8" s="1">
-        <v>40</v>
-      </c>
-      <c r="E8" s="1">
-        <v>48</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>2025</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="1">
+        <v>80</v>
+      </c>
+      <c r="D9" s="1">
+        <v>66</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="1">
-        <v>80</v>
-      </c>
-      <c r="E9" s="1">
-        <v>66</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="1">
+        <v>70</v>
+      </c>
+      <c r="D10" s="1">
+        <v>68</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="1">
-        <v>70</v>
-      </c>
-      <c r="E10" s="1">
-        <v>68</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>18</v>
+      <c r="C11" s="1">
+        <v>110</v>
       </c>
       <c r="D11" s="1">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="E11" s="1">
-        <v>73</v>
-      </c>
-      <c r="F11" s="1">
         <v>1</v>
       </c>
     </row>
